--- a/docs/EPL_Tenders_latest.xlsx
+++ b/docs/EPL_Tenders_latest.xlsx
@@ -12,8 +12,8 @@
     <sheet name="About" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$AF$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Buyer Contacts'!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$AF$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Buyer Contacts'!$A$1:$I$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -691,11 +691,11 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Carbon / Compliance</t>
+          <t>Renewables / BESS / EV</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -705,112 +705,118 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Development of final EPC Wrapper for Scotland</t>
+          <t>CA18436 - Provision of PPA funded Solar PV Roof Array with battery storage</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Scottish Government</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
+          <t>Chichester College Group</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Hayley Abdo</t>
+        </is>
+      </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Paul.packett@gov.scot</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="n"/>
+          <t>support@multiquote.com</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>0151 482 9230</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="4" t="n">
+        <v>900000</v>
+      </c>
       <c r="K2" s="5" t="n">
-        <v>46274.31138888889</v>
+        <v>46274.38763888889</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>46304.45833333334</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M2" s="7">
         <f>IF(L2="","",INT(L2-NOW()))</f>
         <v/>
       </c>
       <c r="N2" s="6" t="n"/>
-      <c r="O2" s="5" t="n"/>
+      <c r="O2" s="5" t="n">
+        <v>46477.95833333334</v>
+      </c>
       <c r="P2" s="2" t="n">
-        <v>180</v>
+        <v>7305</v>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>Open procedure</t>
+          <t>Restricted procedure</t>
         </is>
       </c>
       <c r="R2" s="3" t="n"/>
-      <c r="S2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" s="3" t="n"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Technical (70); price (30)</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>economic (List and brief description of selection criteria: List and brief description of selection criteria: 4B.4 -The bidder co…); technical (List and brief description of selection criteria: List and brief description of selection criteria: 4C.7 - Provide deta…)</t>
-        </is>
-      </c>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n"/>
+      <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>epc</t>
+          <t>battery storage, power purchase agreement, ppa, solar pv</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>71314000, 71314300</t>
+          <t>71314200</t>
         </is>
       </c>
       <c r="Y2" s="8" t="inlineStr">
         <is>
-          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/a4e115c8-447e-4528-9abb-71ac816ec251</t>
         </is>
       </c>
       <c r="Z2" s="8" t="inlineStr">
         <is>
-          <t>https://www.find-tender.service.gov.uk/Notice/085159-2026</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="n"/>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/287ed446-ae14-4b1b-bef8-0fabe8744c07</t>
+        </is>
+      </c>
+      <c r="AA2" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/a4e115c8-447e-4528-9abb-71ac816ec251</t>
+        </is>
+      </c>
       <c r="AB2" s="8" t="inlineStr">
         <is>
-          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
+          <t>https://suppliers.multiquote.com</t>
         </is>
       </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>5 Atlantic Quay, 150 Broomielaw, Glasgow, UKM, G2 8LU</t>
+          <t>Chichester Campus, Westgate Fields, Chichester, PO19 1SB</t>
         </is>
       </c>
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="3" t="inlineStr">
         <is>
-          <t>The Scottish Government has a requirement to place a contract with an external service provider for the provision of Development of final EPC Wrapper for Scotland.</t>
+          <t>The college continues its commitment to reducing emissions and further improving energy efficiency, in alignment with The Association of Colleges Carbon Neutral Agenda. A range of projects are ongoing including the continuing rollout of roof mounted solar arrays using the Power Purchase Agreement (PPA) funding model. This tender is for the provision of a PPA funded Solar PV Array with battery storage option for Haywards Heath College To access this competition: Registered: Login to https://suppliers.multiquote.com and view the opportunity CA18436. Not registered: Visit https://suppliers.multiquote.com then register and quote CA18436 as the reason for registration. Any queries please contact MultiQuote on 020 3920 8054.</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr">
         <is>
-          <t>Find a Tender</t>
+          <t>Contracts Finder</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Renewables / BESS / EV</t>
+          <t>Carbon / Compliance</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -820,42 +826,32 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Measured Term Contract for Combined Re-Roofing, Re-Rendering, EWI and Solar PV Programme</t>
+          <t>Development of final EPC Wrapper for Scotland</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>North Ayrshire Council</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Laura Keane</t>
-        </is>
-      </c>
+          <t>Scottish Government</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>laurakeane@north-ayrshire.gov.uk</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>+44 1294310000</t>
-        </is>
-      </c>
+          <t>Paul.packett@gov.scot</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>UKM93</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>44894399</v>
-      </c>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n"/>
       <c r="K3" s="5" t="n">
-        <v>46290.5117824074</v>
+        <v>46274.31138888889</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>46321.5</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="M3" s="7">
         <f>IF(L3="","",INT(L3-NOW()))</f>
@@ -864,7 +860,7 @@
       <c r="N3" s="6" t="n"/>
       <c r="O3" s="5" t="n"/>
       <c r="P3" s="2" t="n">
-        <v>1080</v>
+        <v>180</v>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
@@ -878,49 +874,49 @@
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Quality (20); Price (80)</t>
+          <t>Technical (70); price (30)</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>suitability (If required, bidders are required to be enrolled in the relevant professional or trade registers within the country in …)</t>
+          <t>economic (List and brief description of selection criteria: List and brief description of selection criteria: 4B.4 -The bidder co…); technical (List and brief description of selection criteria: List and brief description of selection criteria: 4C.7 - Provide deta…)</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>photovoltaic, solar pv</t>
+          <t>epc</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>45260000, 45320000, 50700000, 45261215</t>
+          <t>71314000, 71314300</t>
         </is>
       </c>
       <c r="Y3" s="8" t="inlineStr">
         <is>
-          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
+          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
         </is>
       </c>
       <c r="Z3" s="8" t="inlineStr">
         <is>
-          <t>https://www.find-tender.service.gov.uk/Notice/090994-2026</t>
+          <t>https://www.find-tender.service.gov.uk/Notice/085159-2026</t>
         </is>
       </c>
       <c r="AA3" s="3" t="n"/>
       <c r="AB3" s="8" t="inlineStr">
         <is>
-          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
+          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>Cunninghame House, Friars Croft, Irvine, UKM93, KA12 8EE</t>
+          <t>5 Atlantic Quay, 150 Broomielaw, Glasgow, UKM, G2 8LU</t>
         </is>
       </c>
       <c r="AD3" s="3" t="n"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>North Ayrshire Council ("the Council") invites tenders for the provision of a Measured `Term Contract for a combined re-roofing, re-rendering, external wall insulation and solar photovoltaic (PV) installation programme to residential properties at various locations throughout North Ayrshire. The initial contract period will be three (3) years from the commencement date of 1 April 2027 to 31 March 2030, with the option to extend for up to two (2) additional periods of twelve (12) months each, at the sole discretion of the Council.</t>
+          <t>The Scottish Government has a requirement to place a contract with an external service provider for the provision of Development of final EPC Wrapper for Scotland.</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -931,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -945,235 +941,1032 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>EV Charging Infrastructure</t>
+          <t>​​Renewable Energy Certification Integration in ASEAN​</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>University of Dundee</t>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Stewart Hamilton Kerr</t>
+          <t>Tom Onions</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>s.v.kerr@dundee.ac.uk</t>
+          <t>expertdeployments@ukpact.co.uk</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>+44 1382386810</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>UKM71, Dundee</t>
-        </is>
-      </c>
+          <t>0000000000</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="4" t="n">
         <v>160000</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>46262.66186342593</v>
+        <v>46294.41159722222</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>46300.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="M4" s="7">
         <f>IF(L4="","",INT(L4-NOW()))</f>
         <v/>
       </c>
       <c r="N4" s="6" t="n"/>
-      <c r="O4" s="5" t="n"/>
+      <c r="O4" s="5" t="n">
+        <v>46329</v>
+      </c>
       <c r="P4" s="2" t="n">
-        <v>7200</v>
+        <v>148</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>Open procedure</t>
+          <t>Open procedure (above threshold)</t>
         </is>
       </c>
       <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>Quality (60); price (40)</t>
-        </is>
-      </c>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>charging infrastructure, electric vehicle charging, ev charging</t>
+          <t>decarbonisation, renewable energy</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>50230000, 31158000, 31158100, 34900000, 31600000, 31610000, 34144900, 45311000, 45317000, 50000000</t>
+          <t>09000000</t>
         </is>
       </c>
       <c r="Y4" s="8" t="inlineStr">
         <is>
-          <t>http://www.publiccontractsscotland.gov.uk</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/30ac6008-b80d-41e2-96a1-4fceae17043b</t>
         </is>
       </c>
       <c r="Z4" s="8" t="inlineStr">
         <is>
-          <t>https://www.find-tender.service.gov.uk/Notice/082366-2026</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="n"/>
-      <c r="AB4" s="8" t="inlineStr">
-        <is>
-          <t>http://www.publiccontractsscotland.gov.uk</t>
-        </is>
-      </c>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/072c9766-ef50-4993-9acc-9016a7c75998</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/30ac6008-b80d-41e2-96a1-4fceae17043b https://www.contractsfinder.service.gov.uk/Notice/Attachment/24a31762-7332-4c20-9b9d-a230e4fbe611 https://www.contractsfinder.service.gov.uk/Notice/Attachment/b65eff6c-18b1-4653-93c1-1e943fa44101 https://www.contractsfinder.service.gov.uk/Notice/Attachment/9c23fe19-c029-477c-8048-a7cef0724639</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="n"/>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
+          <t>Second Floor, LONDON, EC1Y8ND</t>
         </is>
       </c>
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>The University require a new Contract for the Supply and maintenance of fully funded EV Charger Infrastructure. The current charge points require upgrading, due to their age and they are out of manufactures warranty. This new Contract opportunity will be for - Supply, Installation and Maintenance of Electric Vehicle Charging Equipment and Associated Items.</t>
+          <t>Palladium as the delivery partner for the Foreign, Commonwealth and Development Office (FCDO) funded UK Partnering for Accelerate Climate Transitions (UK PACT) programme invites you to submit a quotation for the services detailed in this RFQ. Renewable energy has seen a growing demand across the ASEAN region. This is because countries are putting more effort into pursuing energy transition, decarbonisation and net-zero commitments. Renewable energy (RE) certification has emerged as an important market-based tool to facilitate statements and assurance on renewable electricity and support government as well as the private sector in achieving their targets. In addition, RE certification would be a beneficial instrument in supporting the ASEAN Power Grid and the cross-border electricity trading in the region. Interested suppliers/consortia are encouraged to review the RfQ documentation and submit your proposal in accordance with the instructions above by the Close Date and Time. This RFQ includes the following materials: Schedule 1 - Terms of Reference Schedule 2 - Instructions for submission Schedule 3 - Terms and Conditions Annex I - RFQ Response Form Annex II - Budget and workplan template</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>Find a Tender</t>
+          <t>Contracts Finder</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Carbon / Compliance</t>
+          <t>Brokerage / Consultancy</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Net Zero - Retrofit Works (Externals) - Design and Build</t>
+          <t>The Provision of an Energy Portfolio Management System</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Renfrewshire Council</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Kevin Milliken</t>
-        </is>
-      </c>
+          <t>Government Commercial Agency</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>kevin.milliken@renfrewshire.gov.uk</t>
+          <t>info@gca.gov.uk</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>+44 3003000300</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>UKM83, Renfrewshire</t>
-        </is>
-      </c>
+          <t>0345 410 2222</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="4" t="n">
-        <v>135000000</v>
+        <v>1950001</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>46265.35826388889</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>46300.45833333334</v>
-      </c>
+        <v>46296.35194444445</v>
+      </c>
+      <c r="L5" s="6" t="n"/>
       <c r="M5" s="7">
         <f>IF(L5="","",INT(L5-NOW()))</f>
         <v/>
       </c>
       <c r="N5" s="6" t="n"/>
-      <c r="O5" s="5" t="n"/>
+      <c r="O5" s="5" t="n">
+        <v>46295.95833333334</v>
+      </c>
       <c r="P5" s="2" t="n">
-        <v>2520</v>
+        <v>1796</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Restricted procedure</t>
+          <t>Call-off from a dynamic purchasing system</t>
         </is>
       </c>
       <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="3" t="n"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>Quality (60); price (40)</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>suitability (Please refer to the Invitation to Participate Document.)</t>
-        </is>
-      </c>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>net zero</t>
+          <t>meter data</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>45260000, 45320000, 45210000</t>
+          <t>71314000</t>
         </is>
       </c>
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="8" t="inlineStr">
         <is>
-          <t>https://www.find-tender.service.gov.uk/Notice/082401-2026</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/f8acf8f1-d676-4ece-a58e-e60dea73a5c5</t>
         </is>
       </c>
       <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="8" t="inlineStr">
-        <is>
-          <t>https://www.publictenderscotland.publiccontractsscotland.gov.uk/</t>
-        </is>
-      </c>
+      <c r="AB5" s="3" t="n"/>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>Renfrewshire House, Cotton Street, Paisley, UKM83, PA1 1JB</t>
+          <t>39 Old Hall Street, Liverpool, L39PP</t>
         </is>
       </c>
       <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
+          <t>Within the GCA Energy Category, we operate a managed service on behalf of the public sector, aggregating their energy demand and purchasing on the wholesale market under a number of risk strategies. In order to support these activities, we require a cloud-based energy portfolio management solution, suitable for managing the GCA Energy portfolio frameworks, which includes; c.1,200 customers, c.108,000 power / gas meters, c. 80,000 sites There is currently no system in place to meet these requirements. This requirement will run on a 3 month trial period. If after the trial period concludes successfully, the supplier will be awarded the subsequent contract term and value. The value included in this notice is for the trial period only. Any subsequent contract term is subject to further budgetary approval which, will be confirmed at the future procurement stage. The proposed system must be able to accurately record the customer portfolio data for both gas and power, including site and meter information and assigned trading strategy. Each of the meters is assigned to a customer and a site. Each meter is attached to current and future Gas / Power buying strategies with varying buying lengths. The system must support the ability for nominated energy suppliers to access the meter data for their assigned customers. We also require the ability for customers to complete a self-serve audit of their portfolio and buying strategy, including the ability to request changes and additions to t…</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>Contracts Finder</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Renewables / BESS / EV</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Measured Term Contract for Combined Re-Roofing, Re-Rendering, EWI and Solar PV Programme</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>North Ayrshire Council</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Laura Keane</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>laurakeane@north-ayrshire.gov.uk</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>+44 1294310000</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>UKM93</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>44894399</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>46290.5117824074</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>46321.5</v>
+      </c>
+      <c r="M6" s="7">
+        <f>IF(L6="","",INT(L6-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>Open procedure</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Quality (20); Price (80)</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>suitability (If required, bidders are required to be enrolled in the relevant professional or trade registers within the country in …)</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>photovoltaic, solar pv</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>45260000, 45320000, 50700000, 45261215</t>
+        </is>
+      </c>
+      <c r="Y6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
+        </is>
+      </c>
+      <c r="Z6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.find-tender.service.gov.uk/Notice/090994-2026</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Cunninghame House, Friars Croft, Irvine, UKM93, KA12 8EE</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>North Ayrshire Council ("the Council") invites tenders for the provision of a Measured `Term Contract for a combined re-roofing, re-rendering, external wall insulation and solar photovoltaic (PV) installation programme to residential properties at various locations throughout North Ayrshire. The initial contract period will be three (3) years from the commencement date of 1 April 2027 to 31 March 2030, with the option to extend for up to two (2) additional periods of twelve (12) months each, at the sole discretion of the Council.</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>Find a Tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Brokerage / Consultancy</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Children and Young People's Residential Placements Flexible Procurement System (Round 19)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Trafford Council</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Tim Kulewa</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>tim.kulewa@star-procurement.gov.uk</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>+44 1619121616</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1110000000</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>46290.60637731481</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>46325.5</v>
+      </c>
+      <c r="M7" s="7">
+        <f>IF(L7="","",INT(L7-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="5" t="n">
+        <v>46357</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>Open procedure (above threshold)</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>flexible procurement</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>85300000</t>
+        </is>
+      </c>
+      <c r="Y7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9566b75e-d76e-4674-b2fb-59a111017418</t>
+        </is>
+      </c>
+      <c r="Z7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/0ccf08fa-6d39-4244-ba62-9562b0a08b43</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9566b75e-d76e-4674-b2fb-59a111017418 https://procontract.due-north.com/Advert?advertId=72559434-1f29-f111-813c-005056b64545</t>
+        </is>
+      </c>
+      <c r="AB7" s="8" t="inlineStr">
+        <is>
+          <t>http://www.trafford.gov.uk/</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>1st Floor, Trafford Town Hall, Stretford, M32 0TH</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="n"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>The North West Local Authorities are developing a Flexible Procurement System (FPS) to facilitate the commissioning of high quality Children's Residential Placements. We are looking to knowledgeable and experienced providers to work with us to transform the lives of children, enabling them to break down barriers and turn challenging situations into positive ones. Through the FPS we are looking for sustainability, transformation and innovation with providers and Local Authorities and wider partners to work together to ensure each one of our children has the capacity, skills, independence and resilience they will need to meet the challenges of adult life in the 21st century.</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>Contracts Finder</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Energy (CPV match)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Procurement of Solar Power Systems</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Chemonics International, Inc.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Iryna Marochkanych</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>pfruprocurement@chemonics.com</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>+12029553300</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>46295.34738425926</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>46310.375</v>
+      </c>
+      <c r="M8" s="7">
+        <f>IF(L8="","",INT(L8-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="5" t="n">
+        <v>46324.83333333334</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>Open procedure (above threshold)</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" s="3" t="n"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>09330000</t>
+        </is>
+      </c>
+      <c r="Y8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9c6f4687-4df9-405d-be58-e4d18b1fcf2d</t>
+        </is>
+      </c>
+      <c r="Z8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/ca55f98c-34ef-4cbe-b8cc-df90f65c491b</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9c6f4687-4df9-405d-be58-e4d18b1fcf2d https://www.contractsfinder.service.gov.uk/Notice/Attachment/83eead40-7f6a-4075-8811-1c30d44ca654 https://www.contractsfinder.service.gov.uk/Notice/Attachment/8ba4637d-813c-4984-baf2-1f8f7f8418cd https://www.contractsfinder.service.gov.uk/Notice/Attachment/c909b5ee-b213-4123-91d2-da7d18d559ac https://www.contractsfinder.service.gov.uk/Notice/Attachment/5af44e15-014b-47c8-a703-b77b28e2378d</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Ukraine, Kyiv, EC1M 5QL</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Partnership Fund for a Resilient Ukraine Phase 2 (PFRU-2) is a multi-year, multi-donor-funded programme managed by the UK's Foreign, Commonwealth and Development Office. As part of its project activities, PFRU-2 is seeking an organization to supply the Solar Power Systems. Please note the following important tender provisions: • the deadline for submitting proposals is October 15, 2026, at 15:00 Kyiv time; • all questions regarding the tender conditions must be submitted no later than October 09, 2026, at 18:00 Kyiv time; • Price proposals must be submitted either in Ukrainian or English; • All tender-related communication must be conducted exclusively in writing via email at pfruprocurement@chemonics.com; • The PFRU-2 project is exempt from taxes, fees, and VAT in the partner country. Therefore, PFRU-2 will make payments for services excluding VAT; • Email for submitting proposals: pfruprocurement@chemonics.com; • When sending proposals or inquiries via email, it is mandatory to include the tender number PFRU2-2025-779.6 in the email subject line. Proposal Submission Instructions: ITT_PFRU2-2025-779.6 - review the tender conditions; Volume 3_Terms of Reference - complete the document and sign the original scan/convert to PDF and sign electronically and submit the completed Excel file and the signed document as part of the proposal. Annex 1 - complete either the English or Ukrainian version and sign the original and scan/convert to PDF and sign electronically and include it …</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>Contracts Finder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Renewables / BESS / EV</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>EV Charging Infrastructure</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>University of Dundee</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Stewart Hamilton Kerr</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>s.v.kerr@dundee.ac.uk</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>+44 1382386810</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>UKM71, Dundee</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>160000</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>46262.66186342593</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="M9" s="7">
+        <f>IF(L9="","",INT(L9-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>Open procedure</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Quality (60); price (40)</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>charging infrastructure, electric vehicle charging, ev charging</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>50230000, 31158000, 31158100, 34900000, 31600000, 31610000, 34144900, 45311000, 45317000, 50000000</t>
+        </is>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
+      <c r="Z9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.find-tender.service.gov.uk/Notice/082366-2026</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="n"/>
+      <c r="AB9" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="n"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>The University require a new Contract for the Supply and maintenance of fully funded EV Charger Infrastructure. The current charge points require upgrading, due to their age and they are out of manufactures warranty. This new Contract opportunity will be for - Supply, Installation and Maintenance of Electric Vehicle Charging Equipment and Associated Items.</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>Find a Tender</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Carbon / Compliance</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Pakistan NDC 3.0 Delivery Coordination Mechanism (Federal-Provincial Coordination and Tracking)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>targetedfund@ukpact.co.uk</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>46282.40010416666</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>46290.66666666666</v>
+      </c>
+      <c r="M10" s="7">
+        <f>IF(L10="","",INT(L10-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="5" t="n">
+        <v>46327</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>Open procedure (above threshold)</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>greenhouse gas</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>71314000</t>
+        </is>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/f9613a96-8a56-4f2f-b0e6-04b7e416ae1c</t>
+        </is>
+      </c>
+      <c r="Z10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/cb5590f6-5c46-427f-869c-3688e693c300</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/f9613a96-8a56-4f2f-b0e6-04b7e416ae1c https://www.contractsfinder.service.gov.uk/Notice/Attachment/954bd4cc-3272-4d02-91e6-bac3d146d7ba https://www.contractsfinder.service.gov.uk/Notice/Attachment/ff9c8bfd-467b-4f96-b96d-9b13333c8abc https://www.contractsfinder.service.gov.uk/Notice/Attachment/19d894e0-18e8-43a8-9c4c-7c0391dd0f9e</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>16th Floor, Hylo, 105 Bunhill Row, London, EC1Y 8LZ</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="n"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>The UK Government's Partnering for Accelerated Climate Transitions (UK PACT) programme is inviting proposals from qualified suppliers or consortia to deliver technical assistance to the Government of Pakistan. Pakistan has committed to reducing projected greenhouse gas emissions by 50% by 2035 through its Nationally Determined Contribution (NDC) 3.0. Delivering this target will depend heavily on action at the provincial level, where responsibility for many climate-relevant sectors rests. While the Government of Pakistan has established new coordination arrangements through the National Climate Finance Strategy (NCFS), challenges remain around federal-provincial coordination, implementation tracking, climate finance visibility, and reporting progress against national climate commitments. The assignment will provide targeted technical assistance to support the Ministry of Climate Change and Environmental Coordination (MoCC&amp;EC), the Pakistan Climate Change Authority (PCCA), and provincial governments to establish and operationalise a practical federal-provincial coordination and tracking mechanism for NDC 3.0 implementation. The project will strengthen institutional coordination, improve monitoring and reporting of climate actions and investments, build government capacity, and support the mobilisation of climate finance. The intervention will also integrate Gender Equality, Disability and Social Inclusion (GEDSI) considerations to promote more inclusive climate governance and …</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>Contracts Finder</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Energy (CPV match)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Strengthening Carbon Market Readiness and Article 6 Operationalisation in Cameroon</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>targetedfund@ukpact.co.uk</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>46261.62648148148</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>46287.66666666666</v>
+      </c>
+      <c r="M11" s="7">
+        <f>IF(L11="","",INT(L11-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>Open procedure (above threshold)</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>71314000</t>
+        </is>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/04a3aa0a-c3ed-4afc-8b07-4511a46230b3</t>
+        </is>
+      </c>
+      <c r="Z11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/d7504def-9d38-4b6d-8406-f9889eb4a4b6</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/04a3aa0a-c3ed-4afc-8b07-4511a46230b3 https://www.contractsfinder.service.gov.uk/Notice/Attachment/adafe121-5f0d-4423-b5b2-911a032943a0 https://www.contractsfinder.service.gov.uk/Notice/Attachment/b7bcd166-0d2a-456a-84cd-52ba9f7e17a7 https://www.contractsfinder.service.gov.uk/Notice/Attachment/9cac4aa6-4994-4d69-9847-47be5539c20b</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>16th Floor, Hylo, 105 Bunhill Row, London, EC1Y8ND</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>The UK Government's Partnering for Accelerated Climate Transitions (UK PACT) programme is inviting proposals from qualified suppliers or consortia to deliver technical assistance to the Government of Cameroon. Cameroon, situated within the Congo Basin and home to significant forest carbon resources, is seeking to strengthen its readiness to participate in high-integrity international carbon markets, including Article 6 of the Paris Agreement, the Carbon Offsetting and Reduction Scheme for International Aviation (CORSIA), and voluntary carbon markets. While the country has considerable potential to generate climate finance through carbon markets and support implementation of its Nationally Determined Contribution (NDC), key legal, institutional, and operational gaps continue to constrain effective participation. This assignment will provide targeted technical assistance and capacity building to support the Government of Cameroon in establishing the governance frameworks, institutional arrangements, and regulatory systems required to operationalise carbon market participation. Working closely with relevant government institutions, including the Ministry of Environment, Nature Protection and Sustainable Development (MINEPDED), the Ministry of Forestry and Wildlife (MINFOF), the Ministry of Finance (MINFI), and other key stakeholders, the project will strengthen carbon market governance, Article 6 implementation readiness, project approval systems, and institutional coordination…</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>Contracts Finder</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Carbon / Compliance</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Net Zero - Retrofit Works (Externals) - Design and Build</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Renfrewshire Council</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Milliken</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>kevin.milliken@renfrewshire.gov.uk</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>+44 3003000300</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>UKM83, Renfrewshire</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>46265.35826388889</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="M12" s="7">
+        <f>IF(L12="","",INT(L12-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="2" t="n">
+        <v>2520</v>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>Restricted procedure</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Quality (60); price (40)</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>suitability (Please refer to the Invitation to Participate Document.)</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>net zero</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>45260000, 45320000, 45210000</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.find-tender.service.gov.uk/Notice/082401-2026</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="n"/>
+      <c r="AB12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictenderscotland.publiccontractsscotland.gov.uk/</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Renfrewshire House, Cotton Street, Paisley, UKM83, PA1 1JB</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
           <t>This Contract is for the Design, Build and Delivery of retrofit external works to existing wholly owned and mixed-tenure residential properties throughout Renfrewshire. The primary objective is to enhance the energy efficiency and thermal performance of the housing stock. For the initial contract term of 2 years, the Council will provide the design information, using the designs submitted by ECD Architects who were contracted to provide this service. The appointed Contractor will be responsible for the supply and installation of the works only during the initial term. From the commencement of the first extension period, responsibility will transfer to the Contractor, who will undertake both the design and build elements for the remainder of the Contract.</t>
         </is>
       </c>
-      <c r="AF5" s="3" t="inlineStr">
+      <c r="AF12" s="3" t="inlineStr">
         <is>
           <t>Find a Tender</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF5"/>
-  <conditionalFormatting sqref="M2:M5">
+  <autoFilter ref="A1:AF12"/>
+  <conditionalFormatting sqref="M2:M12">
     <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
       <formula>0</formula>
       <formula>14</formula>
@@ -1185,15 +1978,31 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z4" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z9" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z10" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y11" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1205,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1269,182 +2078,406 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>North Ayrshire Council</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Laura Keane</t>
-        </is>
-      </c>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>laurakeane@north-ayrshire.gov.uk</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>+44 1294310000</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
-        </is>
-      </c>
+          <t>targetedfund@ukpact.co.uk</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Cunninghame House, Friars Croft, Irvine, UKM93, KA12 8EE</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>UKM93</t>
-        </is>
-      </c>
+          <t>16th Floor, Hylo, 105 Bunhill Row, London, EC1Y 8LZ</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Measured Term Contract for Combined Re-Roofing, Re-Rendering, EWI and Solar PV Programme</t>
+          <t>Pakistan NDC 3.0 Delivery Coordination Mechanism (Federal-Provincial Coordination and Tracking) | Strengthening Carbon Market Readiness and Article 6 Operationalisation in Cameroon</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Renfrewshire Council</t>
+          <t>Chemonics International, Inc.</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Kevin Milliken</t>
+          <t>Iryna Marochkanych</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>kevin.milliken@renfrewshire.gov.uk</t>
+          <t>pfruprocurement@chemonics.com</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>+44 3003000300</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>https://www.publictenderscotland.publiccontractsscotland.gov.uk/</t>
-        </is>
-      </c>
+          <t>+12029553300</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Renfrewshire House, Cotton Street, Paisley, UKM83, PA1 1JB</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>UKM83, Renfrewshire</t>
-        </is>
-      </c>
+          <t>Ukraine, Kyiv, EC1M 5QL</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Net Zero - Retrofit Works (Externals) - Design and Build</t>
+          <t>Procurement of Solar Power Systems</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Scottish Government</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
+          <t>Chichester College Group</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Hayley Abdo</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Paul.packett@gov.scot</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
+          <t>support@multiquote.com</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0151 482 9230</t>
+        </is>
+      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
+          <t>https://suppliers.multiquote.com</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>5 Atlantic Quay, 150 Broomielaw, Glasgow, UKM, G2 8LU</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
+          <t>Chichester Campus, Westgate Fields, Chichester, PO19 1SB</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Development of final EPC Wrapper for Scotland</t>
+          <t>CA18436 - Provision of PPA funded Solar PV Roof Array with battery storage</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>University of Dundee</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Stewart Hamilton Kerr</t>
-        </is>
-      </c>
+          <t>Government Commercial Agency</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>s.v.kerr@dundee.ac.uk</t>
+          <t>info@gca.gov.uk</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>+44 1382386810</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>http://www.publiccontractsscotland.gov.uk</t>
-        </is>
-      </c>
+          <t>0345 410 2222</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>UKM71, Dundee</t>
-        </is>
-      </c>
+          <t>39 Old Hall Street, Liverpool, L39PP</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>The Provision of an Energy Portfolio Management System</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>North Ayrshire Council</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Laura Keane</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>laurakeane@north-ayrshire.gov.uk</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>+44 1294310000</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Cunninghame House, Friars Croft, Irvine, UKM93, KA12 8EE</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>UKM93</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Measured Term Contract for Combined Re-Roofing, Re-Rendering, EWI and Solar PV Programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Tom Onions</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>expertdeployments@ukpact.co.uk</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>0000000000</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Second Floor, LONDON, EC1Y8ND</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>​​Renewable Energy Certification Integration in ASEAN​</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Renfrewshire Council</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Milliken</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>kevin.milliken@renfrewshire.gov.uk</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>+44 3003000300</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictenderscotland.publiccontractsscotland.gov.uk/</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Renfrewshire House, Cotton Street, Paisley, UKM83, PA1 1JB</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>UKM83, Renfrewshire</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Net Zero - Retrofit Works (Externals) - Design and Build</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Scottish Government</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Paul.packett@gov.scot</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>5 Atlantic Quay, 150 Broomielaw, Glasgow, UKM, G2 8LU</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Development of final EPC Wrapper for Scotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Trafford Council</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Tim Kulewa</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>tim.kulewa@star-procurement.gov.uk</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>+44 1619121616</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>http://www.trafford.gov.uk/</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1st Floor, Trafford Town Hall, Stretford, M32 0TH</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Children and Young People's Residential Placements Flexible Procurement System (Round 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>University of Dundee</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Stewart Hamilton Kerr</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>s.v.kerr@dundee.ac.uk</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>+44 1382386810</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>UKM71, Dundee</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
           <t>EV Charging Infrastructure</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <autoFilter ref="A1:I11"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1471,7 +2504,7 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>05 Oct 2026 14:27</t>
+          <t>06 Oct 2026 06:18</t>
         </is>
       </c>
     </row>
@@ -1528,7 +2561,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">

--- a/docs/EPL_Tenders_latest.xlsx
+++ b/docs/EPL_Tenders_latest.xlsx
@@ -12,8 +12,8 @@
     <sheet name="About" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$AF$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Buyer Contacts'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunities'!$A$1:$AF$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Buyer Contacts'!$A$1:$I$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AF14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Renewables / BESS / EV</t>
+          <t>Solar / BESS / EV</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -765,7 +765,7 @@
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>battery storage, power purchase agreement, ppa, solar pv</t>
+          <t>battery storage, energy efficiency, power purchase agreement, ppa, solar, solar pv</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
@@ -927,11 +927,11 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Renewables / BESS / EV</t>
+          <t>Solar / BESS / EV</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -941,38 +941,38 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>​​Renewable Energy Certification Integration in ASEAN​</t>
+          <t>Procurement of Solar Power Systems</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>PALLADIUM INTERNATIONAL LIMITED</t>
+          <t>Chemonics International, Inc.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Tom Onions</t>
+          <t>Iryna Marochkanych</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>expertdeployments@ukpact.co.uk</t>
+          <t>pfruprocurement@chemonics.com</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>+12029553300</t>
         </is>
       </c>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="4" t="n">
-        <v>160000</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>46294.41159722222</v>
+        <v>46295.34738425926</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>46310.45833333334</v>
+        <v>46310.375</v>
       </c>
       <c r="M4" s="7">
         <f>IF(L4="","",INT(L4-NOW()))</f>
@@ -980,10 +980,10 @@
       </c>
       <c r="N4" s="6" t="n"/>
       <c r="O4" s="5" t="n">
-        <v>46329</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
@@ -1001,39 +1001,39 @@
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>decarbonisation, renewable energy</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>09000000</t>
+          <t>09330000</t>
         </is>
       </c>
       <c r="Y4" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/30ac6008-b80d-41e2-96a1-4fceae17043b</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9c6f4687-4df9-405d-be58-e4d18b1fcf2d</t>
         </is>
       </c>
       <c r="Z4" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/072c9766-ef50-4993-9acc-9016a7c75998</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/ca55f98c-34ef-4cbe-b8cc-df90f65c491b</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/30ac6008-b80d-41e2-96a1-4fceae17043b https://www.contractsfinder.service.gov.uk/Notice/Attachment/24a31762-7332-4c20-9b9d-a230e4fbe611 https://www.contractsfinder.service.gov.uk/Notice/Attachment/b65eff6c-18b1-4653-93c1-1e943fa44101 https://www.contractsfinder.service.gov.uk/Notice/Attachment/9c23fe19-c029-477c-8048-a7cef0724639</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9c6f4687-4df9-405d-be58-e4d18b1fcf2d https://www.contractsfinder.service.gov.uk/Notice/Attachment/83eead40-7f6a-4075-8811-1c30d44ca654 https://www.contractsfinder.service.gov.uk/Notice/Attachment/8ba4637d-813c-4984-baf2-1f8f7f8418cd https://www.contractsfinder.service.gov.uk/Notice/Attachment/c909b5ee-b213-4123-91d2-da7d18d559ac https://www.contractsfinder.service.gov.uk/Notice/Attachment/5af44e15-014b-47c8-a703-b77b28e2378d</t>
         </is>
       </c>
       <c r="AB4" s="3" t="n"/>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>Second Floor, LONDON, EC1Y8ND</t>
+          <t>Ukraine, Kyiv, EC1M 5QL</t>
         </is>
       </c>
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>Palladium as the delivery partner for the Foreign, Commonwealth and Development Office (FCDO) funded UK Partnering for Accelerate Climate Transitions (UK PACT) programme invites you to submit a quotation for the services detailed in this RFQ. Renewable energy has seen a growing demand across the ASEAN region. This is because countries are putting more effort into pursuing energy transition, decarbonisation and net-zero commitments. Renewable energy (RE) certification has emerged as an important market-based tool to facilitate statements and assurance on renewable electricity and support government as well as the private sector in achieving their targets. In addition, RE certification would be a beneficial instrument in supporting the ASEAN Power Grid and the cross-border electricity trading in the region. Interested suppliers/consortia are encouraged to review the RfQ documentation and submit your proposal in accordance with the instructions above by the Close Date and Time. This RFQ includes the following materials: Schedule 1 - Terms of Reference Schedule 2 - Instructions for submission Schedule 3 - Terms and Conditions Annex I - RFQ Response Form Annex II - Budget and workplan template</t>
+          <t>Partnership Fund for a Resilient Ukraine Phase 2 (PFRU-2) is a multi-year, multi-donor-funded programme managed by the UK's Foreign, Commonwealth and Development Office. As part of its project activities, PFRU-2 is seeking an organization to supply the Solar Power Systems. Please note the following important tender provisions: • the deadline for submitting proposals is October 15, 2026, at 15:00 Kyiv time; • all questions regarding the tender conditions must be submitted no later than October 09, 2026, at 18:00 Kyiv time; • Price proposals must be submitted either in Ukrainian or English; • All tender-related communication must be conducted exclusively in writing via email at pfruprocurement@chemonics.com; • The PFRU-2 project is exempt from taxes, fees, and VAT in the partner country. Therefore, PFRU-2 will make payments for services excluding VAT; • Email for submitting proposals: pfruprocurement@chemonics.com; • When sending proposals or inquiries via email, it is mandatory to include the tender number PFRU2-2025-779.6 in the email subject line. Proposal Submission Instructions: ITT_PFRU2-2025-779.6 - review the tender conditions; Volume 3_Terms of Reference - complete the document and sign the original scan/convert to PDF and sign electronically and submit the completed Excel file and the signed document as part of the proposal. Annex 1 - complete either the English or Ukrainian version and sign the original and scan/convert to PDF and sign electronically and include it …</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1044,114 +1044,128 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Brokerage / Consultancy</t>
+          <t>Solar / BESS / EV</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>The Provision of an Energy Portfolio Management System</t>
+          <t>EV Infrastructure Back Office</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Government Commercial Agency</t>
+          <t>Stirling Council</t>
         </is>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>info@gca.gov.uk</t>
+          <t>procurement@stirling.gov.uk</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>0345 410 2222</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n"/>
+          <t>+44 1786404040</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>UKM77</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="n">
-        <v>1950001</v>
+        <v>315000</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>46296.35194444445</v>
-      </c>
-      <c r="L5" s="6" t="n"/>
+        <v>46280.38151620371</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>46310.45833333334</v>
+      </c>
       <c r="M5" s="7">
         <f>IF(L5="","",INT(L5-NOW()))</f>
         <v/>
       </c>
       <c r="N5" s="6" t="n"/>
-      <c r="O5" s="5" t="n">
-        <v>46295.95833333334</v>
-      </c>
+      <c r="O5" s="5" t="n"/>
       <c r="P5" s="2" t="n">
-        <v>1796</v>
+        <v>1080</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Call-off from a dynamic purchasing system</t>
+          <t>Open procedure</t>
         </is>
       </c>
       <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="n"/>
+      <c r="S5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Contract Implementation (20); Account Management (30); Customer Service (30); Reporting Requirements (10); Community Benefits (10); price (60)</t>
+        </is>
+      </c>
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>meter data</t>
+          <t>charge point, charge points, ev infrastructure</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>71314000</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="n"/>
+          <t>65300000, 75100000, 31158000, 72260000, 34144900, 48444100, 50324100, 72267100, 64226000</t>
+        </is>
+      </c>
+      <c r="Y5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
       <c r="Z5" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/f8acf8f1-d676-4ece-a58e-e60dea73a5c5</t>
+          <t>https://www.find-tender.service.gov.uk/Notice/087147-2026</t>
         </is>
       </c>
       <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="3" t="n"/>
+      <c r="AB5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>39 Old Hall Street, Liverpool, L39PP</t>
+          <t>Procurement, Teith House, Stirling, UKM77, FK7 7QA</t>
         </is>
       </c>
       <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>Within the GCA Energy Category, we operate a managed service on behalf of the public sector, aggregating their energy demand and purchasing on the wholesale market under a number of risk strategies. In order to support these activities, we require a cloud-based energy portfolio management solution, suitable for managing the GCA Energy portfolio frameworks, which includes; c.1,200 customers, c.108,000 power / gas meters, c. 80,000 sites There is currently no system in place to meet these requirements. This requirement will run on a 3 month trial period. If after the trial period concludes successfully, the supplier will be awarded the subsequent contract term and value. The value included in this notice is for the trial period only. Any subsequent contract term is subject to further budgetary approval which, will be confirmed at the future procurement stage. The proposed system must be able to accurately record the customer portfolio data for both gas and power, including site and meter information and assigned trading strategy. Each of the meters is assigned to a customer and a site. Each meter is attached to current and future Gas / Power buying strategies with varying buying lengths. The system must support the ability for nominated energy suppliers to access the meter data for their assigned customers. We also require the ability for customers to complete a self-serve audit of their portfolio and buying strategy, including the ability to request changes and additions to t…</t>
+          <t>Stirling Council seeks a Charge Point Network Operator (CPNO) to provide EV Charge Point Management System (CPMS) services for its public and fleet charging network. The contract includes migration from the existing ChargePlace Scotland platform, ongoing operation, customer support, payment processing, monitoring, reporting and account management services for approximately 200 charge points across the Stirling area.</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>Contracts Finder</t>
+          <t>Find a Tender</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Renewables / BESS / EV</t>
+          <t>Carbon / Compliance</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1161,182 +1175,164 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Measured Term Contract for Combined Re-Roofing, Re-Rendering, EWI and Solar PV Programme</t>
+          <t>​​Renewable Energy Certification Integration in ASEAN​</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>North Ayrshire Council</t>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Laura Keane</t>
+          <t>Tom Onions</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>laurakeane@north-ayrshire.gov.uk</t>
+          <t>expertdeployments@ukpact.co.uk</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>+44 1294310000</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>UKM93</t>
-        </is>
-      </c>
+          <t>0000000000</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="4" t="n">
-        <v>44894399</v>
+        <v>160000</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>46290.5117824074</v>
+        <v>46294.41159722222</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>46321.5</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="M6" s="7">
         <f>IF(L6="","",INT(L6-NOW()))</f>
         <v/>
       </c>
       <c r="N6" s="6" t="n"/>
-      <c r="O6" s="5" t="n"/>
+      <c r="O6" s="5" t="n">
+        <v>46329</v>
+      </c>
       <c r="P6" s="2" t="n">
-        <v>1080</v>
+        <v>148</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Open procedure</t>
+          <t>Open procedure (above threshold)</t>
         </is>
       </c>
       <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="3" t="n"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>Quality (20); Price (80)</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>suitability (If required, bidders are required to be enrolled in the relevant professional or trade registers within the country in …)</t>
-        </is>
-      </c>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>photovoltaic, solar pv</t>
+          <t>decarbonisation, net-zero, renewable electricity, renewable energy</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>45260000, 45320000, 50700000, 45261215</t>
+          <t>09000000</t>
         </is>
       </c>
       <c r="Y6" s="8" t="inlineStr">
         <is>
-          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/30ac6008-b80d-41e2-96a1-4fceae17043b</t>
         </is>
       </c>
       <c r="Z6" s="8" t="inlineStr">
         <is>
-          <t>https://www.find-tender.service.gov.uk/Notice/090994-2026</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="8" t="inlineStr">
-        <is>
-          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
-        </is>
-      </c>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/072c9766-ef50-4993-9acc-9016a7c75998</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/30ac6008-b80d-41e2-96a1-4fceae17043b https://www.contractsfinder.service.gov.uk/Notice/Attachment/24a31762-7332-4c20-9b9d-a230e4fbe611 https://www.contractsfinder.service.gov.uk/Notice/Attachment/b65eff6c-18b1-4653-93c1-1e943fa44101 https://www.contractsfinder.service.gov.uk/Notice/Attachment/9c23fe19-c029-477c-8048-a7cef0724639</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="n"/>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>Cunninghame House, Friars Croft, Irvine, UKM93, KA12 8EE</t>
+          <t>Second Floor, LONDON, EC1Y8ND</t>
         </is>
       </c>
       <c r="AD6" s="3" t="n"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>North Ayrshire Council ("the Council") invites tenders for the provision of a Measured `Term Contract for a combined re-roofing, re-rendering, external wall insulation and solar photovoltaic (PV) installation programme to residential properties at various locations throughout North Ayrshire. The initial contract period will be three (3) years from the commencement date of 1 April 2027 to 31 March 2030, with the option to extend for up to two (2) additional periods of twelve (12) months each, at the sole discretion of the Council.</t>
+          <t>Palladium as the delivery partner for the Foreign, Commonwealth and Development Office (FCDO) funded UK Partnering for Accelerate Climate Transitions (UK PACT) programme invites you to submit a quotation for the services detailed in this RFQ. Renewable energy has seen a growing demand across the ASEAN region. This is because countries are putting more effort into pursuing energy transition, decarbonisation and net-zero commitments. Renewable energy (RE) certification has emerged as an important market-based tool to facilitate statements and assurance on renewable electricity and support government as well as the private sector in achieving their targets. In addition, RE certification would be a beneficial instrument in supporting the ASEAN Power Grid and the cross-border electricity trading in the region. Interested suppliers/consortia are encouraged to review the RfQ documentation and submit your proposal in accordance with the instructions above by the Close Date and Time. This RFQ includes the following materials: Schedule 1 - Terms of Reference Schedule 2 - Instructions for submission Schedule 3 - Terms and Conditions Annex I - RFQ Response Form Annex II - Budget and workplan template</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>Find a Tender</t>
+          <t>Contracts Finder</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Brokerage / Consultancy</t>
+          <t>Metering / Energy Management</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Children and Young People's Residential Placements Flexible Procurement System (Round 19)</t>
+          <t>The Provision of an Energy Portfolio Management System</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Trafford Council</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Tim Kulewa</t>
-        </is>
-      </c>
+          <t>Government Commercial Agency</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>tim.kulewa@star-procurement.gov.uk</t>
+          <t>info@gca.gov.uk</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>+44 1619121616</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
+          <t>0345 410 2222</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="4" t="n">
-        <v>1110000000</v>
+        <v>1950001</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>46290.60637731481</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>46325.5</v>
-      </c>
+        <v>46296.35194444445</v>
+      </c>
+      <c r="L7" s="6" t="n"/>
       <c r="M7" s="7">
         <f>IF(L7="","",INT(L7-NOW()))</f>
         <v/>
       </c>
       <c r="N7" s="6" t="n"/>
       <c r="O7" s="5" t="n">
-        <v>46357</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>396</v>
+        <v>1796</v>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Open procedure (above threshold)</t>
+          <t>Call-off from a dynamic purchasing system</t>
         </is>
       </c>
       <c r="R7" s="3" t="n"/>
@@ -1350,43 +1346,31 @@
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>flexible procurement</t>
+          <t>meter data, renewables</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>85300000</t>
-        </is>
-      </c>
-      <c r="Y7" s="8" t="inlineStr">
-        <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/9566b75e-d76e-4674-b2fb-59a111017418</t>
-        </is>
-      </c>
+          <t>71314000</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/0ccf08fa-6d39-4244-ba62-9562b0a08b43</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/9566b75e-d76e-4674-b2fb-59a111017418 https://procontract.due-north.com/Advert?advertId=72559434-1f29-f111-813c-005056b64545</t>
-        </is>
-      </c>
-      <c r="AB7" s="8" t="inlineStr">
-        <is>
-          <t>http://www.trafford.gov.uk/</t>
-        </is>
-      </c>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/f8acf8f1-d676-4ece-a58e-e60dea73a5c5</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>1st Floor, Trafford Town Hall, Stretford, M32 0TH</t>
+          <t>39 Old Hall Street, Liverpool, L39PP</t>
         </is>
       </c>
       <c r="AD7" s="3" t="n"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>The North West Local Authorities are developing a Flexible Procurement System (FPS) to facilitate the commissioning of high quality Children's Residential Placements. We are looking to knowledgeable and experienced providers to work with us to transform the lives of children, enabling them to break down barriers and turn challenging situations into positive ones. Through the FPS we are looking for sustainability, transformation and innovation with providers and Local Authorities and wider partners to work together to ensure each one of our children has the capacity, skills, independence and resilience they will need to meet the challenges of adult life in the 21st century.</t>
+          <t>Within the GCA Energy Category, we operate a managed service on behalf of the public sector, aggregating their energy demand and purchasing on the wholesale market under a number of risk strategies. In order to support these activities, we require a cloud-based energy portfolio management solution, suitable for managing the GCA Energy portfolio frameworks, which includes; c.1,200 customers, c.108,000 power / gas meters, c. 80,000 sites There is currently no system in place to meet these requirements. This requirement will run on a 3 month trial period. If after the trial period concludes successfully, the supplier will be awarded the subsequent contract term and value. The value included in this notice is for the trial period only. Any subsequent contract term is subject to further budgetary approval which, will be confirmed at the future procurement stage. The proposed system must be able to accurately record the customer portfolio data for both gas and power, including site and meter information and assigned trading strategy. Each of the meters is assigned to a customer and a site. Each meter is attached to current and future Gas / Power buying strategies with varying buying lengths. The system must support the ability for nominated energy suppliers to access the meter data for their assigned customers. We also require the ability for customers to complete a self-serve audit of their portfolio and buying strategy, including the ability to request changes and additions to t…</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1397,11 +1381,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Energy (CPV match)</t>
+          <t>Solar / BESS / EV</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1411,110 +1395,116 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Procurement of Solar Power Systems</t>
+          <t>Partick Housing Association - Gutter Cleaning, Solar Cleaning &amp; Roof Inspection Works (2026-2029)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Chemonics International, Inc.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Iryna Marochkanych</t>
-        </is>
-      </c>
+          <t>Partick Housing Association Ltd.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>pfruprocurement@chemonics.com</t>
+          <t>CHowe@partickha.org.uk</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>+12029553300</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>+44 1413573773</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>UKM82, Partick.</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="n"/>
       <c r="K8" s="5" t="n">
-        <v>46295.34738425926</v>
+        <v>46272.60097222222</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>46310.375</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M8" s="7">
         <f>IF(L8="","",INT(L8-NOW()))</f>
         <v/>
       </c>
       <c r="N8" s="6" t="n"/>
-      <c r="O8" s="5" t="n">
-        <v>46324.83333333334</v>
-      </c>
+      <c r="O8" s="5" t="n"/>
       <c r="P8" s="2" t="n">
-        <v>62</v>
+        <v>1080</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Open procedure (above threshold)</t>
+          <t>Open procedure</t>
         </is>
       </c>
       <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
+      <c r="S8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Quality (40%); price (60%)</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>suitability (The relevant requirement is set out in the SPD, Part IV Selection Criteria [4A1a] Enrolment in a relevant professional …)</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>09330000</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Y8" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/9c6f4687-4df9-405d-be58-e4d18b1fcf2d</t>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
         </is>
       </c>
       <c r="Z8" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/ca55f98c-34ef-4cbe-b8cc-df90f65c491b</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/9c6f4687-4df9-405d-be58-e4d18b1fcf2d https://www.contractsfinder.service.gov.uk/Notice/Attachment/83eead40-7f6a-4075-8811-1c30d44ca654 https://www.contractsfinder.service.gov.uk/Notice/Attachment/8ba4637d-813c-4984-baf2-1f8f7f8418cd https://www.contractsfinder.service.gov.uk/Notice/Attachment/c909b5ee-b213-4123-91d2-da7d18d559ac https://www.contractsfinder.service.gov.uk/Notice/Attachment/5af44e15-014b-47c8-a703-b77b28e2378d</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n"/>
+          <t>https://www.find-tender.service.gov.uk/Notice/084524-2026</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="n"/>
+      <c r="AB8" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>Ukraine, Kyiv, EC1M 5QL</t>
+          <t>10 Mansfield Street, Glasgow, UKM82, G11 5QP</t>
         </is>
       </c>
       <c r="AD8" s="3" t="n"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>Partnership Fund for a Resilient Ukraine Phase 2 (PFRU-2) is a multi-year, multi-donor-funded programme managed by the UK's Foreign, Commonwealth and Development Office. As part of its project activities, PFRU-2 is seeking an organization to supply the Solar Power Systems. Please note the following important tender provisions: • the deadline for submitting proposals is October 15, 2026, at 15:00 Kyiv time; • all questions regarding the tender conditions must be submitted no later than October 09, 2026, at 18:00 Kyiv time; • Price proposals must be submitted either in Ukrainian or English; • All tender-related communication must be conducted exclusively in writing via email at pfruprocurement@chemonics.com; • The PFRU-2 project is exempt from taxes, fees, and VAT in the partner country. Therefore, PFRU-2 will make payments for services excluding VAT; • Email for submitting proposals: pfruprocurement@chemonics.com; • When sending proposals or inquiries via email, it is mandatory to include the tender number PFRU2-2025-779.6 in the email subject line. Proposal Submission Instructions: ITT_PFRU2-2025-779.6 - review the tender conditions; Volume 3_Terms of Reference - complete the document and sign the original scan/convert to PDF and sign electronically and submit the completed Excel file and the signed document as part of the proposal. Annex 1 - complete either the English or Ukrainian version and sign the original and scan/convert to PDF and sign electronically and include it …</t>
+          <t>The provision of gutter cleaning, solar cleaning and roof inspection works and slope mounted anchor inspection works. The contract period will be for 36 months. The programme of gutter cleaning, solar cleaning and inspections should commence within the first month of the contract.</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>Contracts Finder</t>
+          <t>Find a Tender</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Renewables / BESS / EV</t>
+          <t>Energy Procurement / Brokerage</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1524,118 +1514,122 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>EV Charging Infrastructure</t>
+          <t>Children and Young People's Residential Placements Flexible Procurement System (Round 19)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>University of Dundee</t>
+          <t>Trafford Council</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Stewart Hamilton Kerr</t>
+          <t>Tim Kulewa</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>s.v.kerr@dundee.ac.uk</t>
+          <t>tim.kulewa@star-procurement.gov.uk</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>+44 1382386810</t>
+          <t>+44 1619121616</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>UKM71, Dundee</t>
+          <t>England</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>160000</v>
+        <v>1110000000</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>46262.66186342593</v>
+        <v>46290.60637731481</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>46300.45833333334</v>
+        <v>46325.5</v>
       </c>
       <c r="M9" s="7">
         <f>IF(L9="","",INT(L9-NOW()))</f>
         <v/>
       </c>
       <c r="N9" s="6" t="n"/>
-      <c r="O9" s="5" t="n"/>
+      <c r="O9" s="5" t="n">
+        <v>46357</v>
+      </c>
       <c r="P9" s="2" t="n">
-        <v>7200</v>
+        <v>396</v>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>Open procedure</t>
+          <t>Open procedure (above threshold)</t>
         </is>
       </c>
       <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="3" t="n"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>Quality (60); price (40)</t>
-        </is>
-      </c>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>charging infrastructure, electric vehicle charging, ev charging</t>
+          <t>flexible procurement</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>50230000, 31158000, 31158100, 34900000, 31600000, 31610000, 34144900, 45311000, 45317000, 50000000</t>
+          <t>85300000</t>
         </is>
       </c>
       <c r="Y9" s="8" t="inlineStr">
         <is>
-          <t>http://www.publiccontractsscotland.gov.uk</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9566b75e-d76e-4674-b2fb-59a111017418</t>
         </is>
       </c>
       <c r="Z9" s="8" t="inlineStr">
         <is>
-          <t>https://www.find-tender.service.gov.uk/Notice/082366-2026</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="n"/>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/0ccf08fa-6d39-4244-ba62-9562b0a08b43</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/9566b75e-d76e-4674-b2fb-59a111017418 https://procontract.due-north.com/Advert?advertId=72559434-1f29-f111-813c-005056b64545</t>
+        </is>
+      </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
-          <t>http://www.publiccontractsscotland.gov.uk</t>
+          <t>http://www.trafford.gov.uk/</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
+          <t>1st Floor, Trafford Town Hall, Stretford, M32 0TH</t>
         </is>
       </c>
       <c r="AD9" s="3" t="n"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>The University require a new Contract for the Supply and maintenance of fully funded EV Charger Infrastructure. The current charge points require upgrading, due to their age and they are out of manufactures warranty. This new Contract opportunity will be for - Supply, Installation and Maintenance of Electric Vehicle Charging Equipment and Associated Items.</t>
+          <t>The North West Local Authorities are developing a Flexible Procurement System (FPS) to facilitate the commissioning of high quality Children's Residential Placements. We are looking to knowledgeable and experienced providers to work with us to transform the lives of children, enabling them to break down barriers and turn challenging situations into positive ones. Through the FPS we are looking for sustainability, transformation and innovation with providers and Local Authorities and wider partners to work together to ensure each one of our children has the capacity, skills, independence and resilience they will need to meet the challenges of adult life in the 21st century.</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>Find a Tender</t>
+          <t>Contracts Finder</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Carbon / Compliance</t>
+          <t>Solar / BESS / EV</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1645,106 +1639,118 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Pakistan NDC 3.0 Delivery Coordination Mechanism (Federal-Provincial Coordination and Tracking)</t>
+          <t>EV Charging Infrastructure</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>PALLADIUM INTERNATIONAL LIMITED</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n"/>
+          <t>University of Dundee</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Stewart Hamilton Kerr</t>
+        </is>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>targetedfund@ukpact.co.uk</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+          <t>s.v.kerr@dundee.ac.uk</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>+44 1382386810</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>UKM71, Dundee</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="n">
-        <v>250000</v>
+        <v>160000</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>46282.40010416666</v>
+        <v>46262.66186342593</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>46290.66666666666</v>
+        <v>46300.45833333334</v>
       </c>
       <c r="M10" s="7">
         <f>IF(L10="","",INT(L10-NOW()))</f>
         <v/>
       </c>
       <c r="N10" s="6" t="n"/>
-      <c r="O10" s="5" t="n">
-        <v>46327</v>
-      </c>
+      <c r="O10" s="5" t="n"/>
       <c r="P10" s="2" t="n">
-        <v>363</v>
+        <v>7200</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Open procedure (above threshold)</t>
+          <t>Open procedure</t>
         </is>
       </c>
       <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="n"/>
+      <c r="S10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Quality (60); price (40)</t>
+        </is>
+      </c>
       <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>greenhouse gas</t>
+          <t>charge points, charging infrastructure, electric vehicle charging, ev charging</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>71314000</t>
+          <t>50230000, 31158000, 31158100, 34900000, 31600000, 31610000, 34144900, 45311000, 45317000, 50000000</t>
         </is>
       </c>
       <c r="Y10" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/f9613a96-8a56-4f2f-b0e6-04b7e416ae1c</t>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
         </is>
       </c>
       <c r="Z10" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/cb5590f6-5c46-427f-869c-3688e693c300</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/f9613a96-8a56-4f2f-b0e6-04b7e416ae1c https://www.contractsfinder.service.gov.uk/Notice/Attachment/954bd4cc-3272-4d02-91e6-bac3d146d7ba https://www.contractsfinder.service.gov.uk/Notice/Attachment/ff9c8bfd-467b-4f96-b96d-9b13333c8abc https://www.contractsfinder.service.gov.uk/Notice/Attachment/19d894e0-18e8-43a8-9c4c-7c0391dd0f9e</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n"/>
+          <t>https://www.find-tender.service.gov.uk/Notice/082366-2026</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="n"/>
+      <c r="AB10" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>16th Floor, Hylo, 105 Bunhill Row, London, EC1Y 8LZ</t>
+          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
         </is>
       </c>
       <c r="AD10" s="3" t="n"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>The UK Government's Partnering for Accelerated Climate Transitions (UK PACT) programme is inviting proposals from qualified suppliers or consortia to deliver technical assistance to the Government of Pakistan. Pakistan has committed to reducing projected greenhouse gas emissions by 50% by 2035 through its Nationally Determined Contribution (NDC) 3.0. Delivering this target will depend heavily on action at the provincial level, where responsibility for many climate-relevant sectors rests. While the Government of Pakistan has established new coordination arrangements through the National Climate Finance Strategy (NCFS), challenges remain around federal-provincial coordination, implementation tracking, climate finance visibility, and reporting progress against national climate commitments. The assignment will provide targeted technical assistance to support the Ministry of Climate Change and Environmental Coordination (MoCC&amp;EC), the Pakistan Climate Change Authority (PCCA), and provincial governments to establish and operationalise a practical federal-provincial coordination and tracking mechanism for NDC 3.0 implementation. The project will strengthen institutional coordination, improve monitoring and reporting of climate actions and investments, build government capacity, and support the mobilisation of climate finance. The intervention will also integrate Gender Equality, Disability and Social Inclusion (GEDSI) considerations to promote more inclusive climate governance and …</t>
+          <t>The University require a new Contract for the Supply and maintenance of fully funded EV Charger Infrastructure. The current charge points require upgrading, due to their age and they are out of manufactures warranty. This new Contract opportunity will be for - Supply, Installation and Maintenance of Electric Vehicle Charging Equipment and Associated Items.</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>Contracts Finder</t>
+          <t>Find a Tender</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Energy (CPV match)</t>
+          <t>Carbon / Compliance</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1754,30 +1760,42 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Strengthening Carbon Market Readiness and Article 6 Operationalisation in Cameroon</t>
+          <t>Non-Domestic EPCs</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>PALLADIUM INTERNATIONAL LIMITED</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n"/>
+          <t>Rochdale Boroughwide Housing</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Lewis Tomlinson</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>targetedfund@ukpact.co.uk</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+          <t>Lewis.Tomlinson@rbh.org.uk</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>+44 1706273778</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="n">
-        <v>300000</v>
+        <v>25000</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>46261.62648148148</v>
+        <v>46269.38744212963</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>46287.66666666666</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M11" s="7">
         <f>IF(L11="","",INT(L11-NOW()))</f>
@@ -1785,14 +1803,14 @@
       </c>
       <c r="N11" s="6" t="n"/>
       <c r="O11" s="5" t="n">
-        <v>46321</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>339</v>
+        <v>731</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Open procedure (above threshold)</t>
+          <t>Open procedure (below threshold)</t>
         </is>
       </c>
       <c r="R11" s="3" t="n"/>
@@ -1804,37 +1822,45 @@
       </c>
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>energy performance certificates, epc, epcs</t>
+        </is>
+      </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>71314000</t>
+          <t>73000000</t>
         </is>
       </c>
       <c r="Y11" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/04a3aa0a-c3ed-4afc-8b07-4511a46230b3</t>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/c684c2d3-71be-4a22-bea1-56816b71f563</t>
         </is>
       </c>
       <c r="Z11" s="8" t="inlineStr">
         <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/d7504def-9d38-4b6d-8406-f9889eb4a4b6</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.contractsfinder.service.gov.uk/Notice/04a3aa0a-c3ed-4afc-8b07-4511a46230b3 https://www.contractsfinder.service.gov.uk/Notice/Attachment/adafe121-5f0d-4423-b5b2-911a032943a0 https://www.contractsfinder.service.gov.uk/Notice/Attachment/b7bcd166-0d2a-456a-84cd-52ba9f7e17a7 https://www.contractsfinder.service.gov.uk/Notice/Attachment/9cac4aa6-4994-4d69-9847-47be5539c20b</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n"/>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/be55a7c0-3588-49be-8500-1fd682981669</t>
+        </is>
+      </c>
+      <c r="AA11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/c684c2d3-71be-4a22-bea1-56816b71f563</t>
+        </is>
+      </c>
+      <c r="AB11" s="8" t="inlineStr">
+        <is>
+          <t>http://www.rbhousing.org.uk/</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>16th Floor, Hylo, 105 Bunhill Row, London, EC1Y8ND</t>
+          <t>Unique Enterprise Centre, Rochdale, OL162UP</t>
         </is>
       </c>
       <c r="AD11" s="3" t="n"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>The UK Government's Partnering for Accelerated Climate Transitions (UK PACT) programme is inviting proposals from qualified suppliers or consortia to deliver technical assistance to the Government of Cameroon. Cameroon, situated within the Congo Basin and home to significant forest carbon resources, is seeking to strengthen its readiness to participate in high-integrity international carbon markets, including Article 6 of the Paris Agreement, the Carbon Offsetting and Reduction Scheme for International Aviation (CORSIA), and voluntary carbon markets. While the country has considerable potential to generate climate finance through carbon markets and support implementation of its Nationally Determined Contribution (NDC), key legal, institutional, and operational gaps continue to constrain effective participation. This assignment will provide targeted technical assistance and capacity building to support the Government of Cameroon in establishing the governance frameworks, institutional arrangements, and regulatory systems required to operationalise carbon market participation. Working closely with relevant government institutions, including the Ministry of Environment, Nature Protection and Sustainable Development (MINEPDED), the Ministry of Forestry and Wildlife (MINFOF), the Ministry of Finance (MINFI), and other key stakeholders, the project will strengthen carbon market governance, Article 6 implementation readiness, project approval systems, and institutional coordination…</t>
+          <t>Non-Domestic EPCs RBH are looking for a supplier that can carry out non-domestic Energy Performance Certificates (EPC's) for properties within the society's portfolio. This will include but is not limited to shops, community centres, community bases, offices, stores. In carrying out this service, RBH will require • A prompt response/acknowledgement to email instructions (within 2 working days). • To arrange appointments directly with customer (if occupied) within 2 working days of instruction. • Prompt collection and return of keys from RBH office/hubs within the following postcode areas (OL10, OL11, OL12, OL15, OL16, M24, BL9). • EPC lodgement within 5 days of access to the property. • Provide link to lodged EPC and copy of XML file via email within 5 working days of EPC lodgement.</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -1845,7 +1871,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1859,114 +1885,328 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Net Zero - Retrofit Works (Externals) - Design and Build</t>
+          <t>Pakistan NDC 3.0 Delivery Coordination Mechanism (Federal-Provincial Coordination and Tracking)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Renfrewshire Council</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Kevin Milliken</t>
-        </is>
-      </c>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>kevin.milliken@renfrewshire.gov.uk</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>+44 3003000300</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>UKM83, Renfrewshire</t>
-        </is>
-      </c>
+          <t>targetedfund@ukpact.co.uk</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="4" t="n">
-        <v>135000000</v>
+        <v>250000</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>46265.35826388889</v>
+        <v>46282.40010416666</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>46300.45833333334</v>
+        <v>46290.66666666666</v>
       </c>
       <c r="M12" s="7">
         <f>IF(L12="","",INT(L12-NOW()))</f>
         <v/>
       </c>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="5" t="n"/>
+      <c r="O12" s="5" t="n">
+        <v>46327</v>
+      </c>
       <c r="P12" s="2" t="n">
-        <v>2520</v>
+        <v>363</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>Restricted procedure</t>
+          <t>Open procedure (above threshold)</t>
         </is>
       </c>
       <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" s="3" t="n"/>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>Quality (60); price (40)</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>suitability (Please refer to the Invitation to Participate Document.)</t>
-        </is>
-      </c>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>net zero</t>
+          <t>greenhouse gas</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>45260000, 45320000, 45210000</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="n"/>
+          <t>71314000</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/f9613a96-8a56-4f2f-b0e6-04b7e416ae1c</t>
+        </is>
+      </c>
       <c r="Z12" s="8" t="inlineStr">
         <is>
-          <t>https://www.find-tender.service.gov.uk/Notice/082401-2026</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="n"/>
-      <c r="AB12" s="8" t="inlineStr">
-        <is>
-          <t>https://www.publictenderscotland.publiccontractsscotland.gov.uk/</t>
-        </is>
-      </c>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/cb5590f6-5c46-427f-869c-3688e693c300</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/f9613a96-8a56-4f2f-b0e6-04b7e416ae1c https://www.contractsfinder.service.gov.uk/Notice/Attachment/954bd4cc-3272-4d02-91e6-bac3d146d7ba https://www.contractsfinder.service.gov.uk/Notice/Attachment/ff9c8bfd-467b-4f96-b96d-9b13333c8abc https://www.contractsfinder.service.gov.uk/Notice/Attachment/19d894e0-18e8-43a8-9c4c-7c0391dd0f9e</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="n"/>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>Renfrewshire House, Cotton Street, Paisley, UKM83, PA1 1JB</t>
+          <t>16th Floor, Hylo, 105 Bunhill Row, London, EC1Y 8LZ</t>
         </is>
       </c>
       <c r="AD12" s="3" t="n"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
+          <t>The UK Government's Partnering for Accelerated Climate Transitions (UK PACT) programme is inviting proposals from qualified suppliers or consortia to deliver technical assistance to the Government of Pakistan. Pakistan has committed to reducing projected greenhouse gas emissions by 50% by 2035 through its Nationally Determined Contribution (NDC) 3.0. Delivering this target will depend heavily on action at the provincial level, where responsibility for many climate-relevant sectors rests. While the Government of Pakistan has established new coordination arrangements through the National Climate Finance Strategy (NCFS), challenges remain around federal-provincial coordination, implementation tracking, climate finance visibility, and reporting progress against national climate commitments. The assignment will provide targeted technical assistance to support the Ministry of Climate Change and Environmental Coordination (MoCC&amp;EC), the Pakistan Climate Change Authority (PCCA), and provincial governments to establish and operationalise a practical federal-provincial coordination and tracking mechanism for NDC 3.0 implementation. The project will strengthen institutional coordination, improve monitoring and reporting of climate actions and investments, build government capacity, and support the mobilisation of climate finance. The intervention will also integrate Gender Equality, Disability and Social Inclusion (GEDSI) considerations to promote more inclusive climate governance and …</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>Contracts Finder</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Energy (CPV match)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Strengthening Carbon Market Readiness and Article 6 Operationalisation in Cameroon</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>targetedfund@ukpact.co.uk</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>46261.62648148148</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>46287.66666666666</v>
+      </c>
+      <c r="M13" s="7">
+        <f>IF(L13="","",INT(L13-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>Open procedure (above threshold)</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>71314000</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/04a3aa0a-c3ed-4afc-8b07-4511a46230b3</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/d7504def-9d38-4b6d-8406-f9889eb4a4b6</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.contractsfinder.service.gov.uk/Notice/04a3aa0a-c3ed-4afc-8b07-4511a46230b3 https://www.contractsfinder.service.gov.uk/Notice/Attachment/adafe121-5f0d-4423-b5b2-911a032943a0 https://www.contractsfinder.service.gov.uk/Notice/Attachment/b7bcd166-0d2a-456a-84cd-52ba9f7e17a7 https://www.contractsfinder.service.gov.uk/Notice/Attachment/9cac4aa6-4994-4d69-9847-47be5539c20b</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>16th Floor, Hylo, 105 Bunhill Row, London, EC1Y8ND</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="n"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>The UK Government's Partnering for Accelerated Climate Transitions (UK PACT) programme is inviting proposals from qualified suppliers or consortia to deliver technical assistance to the Government of Cameroon. Cameroon, situated within the Congo Basin and home to significant forest carbon resources, is seeking to strengthen its readiness to participate in high-integrity international carbon markets, including Article 6 of the Paris Agreement, the Carbon Offsetting and Reduction Scheme for International Aviation (CORSIA), and voluntary carbon markets. While the country has considerable potential to generate climate finance through carbon markets and support implementation of its Nationally Determined Contribution (NDC), key legal, institutional, and operational gaps continue to constrain effective participation. This assignment will provide targeted technical assistance and capacity building to support the Government of Cameroon in establishing the governance frameworks, institutional arrangements, and regulatory systems required to operationalise carbon market participation. Working closely with relevant government institutions, including the Ministry of Environment, Nature Protection and Sustainable Development (MINEPDED), the Ministry of Forestry and Wildlife (MINFOF), the Ministry of Finance (MINFI), and other key stakeholders, the project will strengthen carbon market governance, Article 6 implementation readiness, project approval systems, and institutional coordination…</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>Contracts Finder</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Carbon / Compliance</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Net Zero - Retrofit Works (Externals) - Design and Build</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Renfrewshire Council</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Milliken</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>kevin.milliken@renfrewshire.gov.uk</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>+44 3003000300</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>UKM83, Renfrewshire</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>46265.35826388889</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="M14" s="7">
+        <f>IF(L14="","",INT(L14-NOW()))</f>
+        <v/>
+      </c>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="2" t="n">
+        <v>2520</v>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>Restricted procedure</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Quality (60); price (40)</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>suitability (Please refer to the Invitation to Participate Document.)</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>energy efficiency, net zero</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>45260000, 45320000, 45210000</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="n"/>
+      <c r="Z14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.find-tender.service.gov.uk/Notice/082401-2026</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="n"/>
+      <c r="AB14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.publictenderscotland.publiccontractsscotland.gov.uk/</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Renfrewshire House, Cotton Street, Paisley, UKM83, PA1 1JB</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="n"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
           <t>This Contract is for the Design, Build and Delivery of retrofit external works to existing wholly owned and mixed-tenure residential properties throughout Renfrewshire. The primary objective is to enhance the energy efficiency and thermal performance of the housing stock. For the initial contract term of 2 years, the Council will provide the design information, using the designs submitted by ECD Architects who were contracted to provide this service. The appointed Contractor will be responsible for the supply and installation of the works only during the initial term. From the commencement of the first extension period, responsibility will transfer to the Contractor, who will undertake both the design and build elements for the remainder of the Contract.</t>
         </is>
       </c>
-      <c r="AF12" s="3" t="inlineStr">
+      <c r="AF14" s="3" t="inlineStr">
         <is>
           <t>Find a Tender</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF12"/>
-  <conditionalFormatting sqref="M2:M12">
+  <autoFilter ref="A1:AF14"/>
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
       <formula>0</formula>
       <formula>14</formula>
@@ -1985,24 +2225,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z6" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z6" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z7" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y8" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y9" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z9" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y10" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z10" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y11" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z11" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z12" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z11" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA11" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y12" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z12" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y13" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z13" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z14" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2014,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2218,82 +2465,78 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>North Ayrshire Council</t>
+          <t>PALLADIUM INTERNATIONAL LIMITED</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Laura Keane</t>
+          <t>Tom Onions</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>laurakeane@north-ayrshire.gov.uk</t>
+          <t>expertdeployments@ukpact.co.uk</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>+44 1294310000</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk/web/login.html</t>
-        </is>
-      </c>
+          <t>0000000000</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Cunninghame House, Friars Croft, Irvine, UKM93, KA12 8EE</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>UKM93</t>
-        </is>
-      </c>
+          <t>Second Floor, LONDON, EC1Y8ND</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Measured Term Contract for Combined Re-Roofing, Re-Rendering, EWI and Solar PV Programme</t>
+          <t>​​Renewable Energy Certification Integration in ASEAN​</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PALLADIUM INTERNATIONAL LIMITED</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Tom Onions</t>
-        </is>
-      </c>
+          <t>Partick Housing Association Ltd.</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>expertdeployments@ukpact.co.uk</t>
+          <t>CHowe@partickha.org.uk</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0000000000</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n"/>
+          <t>+44 1413573773</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Second Floor, LONDON, EC1Y8ND</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n"/>
+          <t>10 Mansfield Street, Glasgow, UKM82, G11 5QP</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>UKM82, Partick.</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>​​Renewable Energy Certification Integration in ASEAN​</t>
+          <t>Partick Housing Association - Gutter Cleaning, Solar Cleaning &amp; Roof Inspection Works (2026-2029)</t>
         </is>
       </c>
     </row>
@@ -2345,29 +2588,37 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Scottish Government</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
+          <t>Rochdale Boroughwide Housing</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Lewis Tomlinson</t>
+        </is>
+      </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Paul.packett@gov.scot</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
+          <t>Lewis.Tomlinson@rbh.org.uk</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>+44 1706273778</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
+          <t>http://www.rbhousing.org.uk/</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>5 Atlantic Quay, 150 Broomielaw, Glasgow, UKM, G2 8LU</t>
+          <t>Unique Enterprise Centre, Rochdale, OL162UP</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>England</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -2375,44 +2626,36 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Development of final EPC Wrapper for Scotland</t>
+          <t>Non-Domestic EPCs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Trafford Council</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Tim Kulewa</t>
-        </is>
-      </c>
+          <t>Scottish Government</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>tim.kulewa@star-procurement.gov.uk</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>+44 1619121616</t>
-        </is>
-      </c>
+          <t>Paul.packett@gov.scot</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>http://www.trafford.gov.uk/</t>
+          <t>http://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1st Floor, Trafford Town Hall, Stretford, M32 0TH</t>
+          <t>5 Atlantic Quay, 150 Broomielaw, Glasgow, UKM, G2 8LU</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -2420,44 +2663,40 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Children and Young People's Residential Placements Flexible Procurement System (Round 19)</t>
+          <t>Development of final EPC Wrapper for Scotland</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>University of Dundee</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Stewart Hamilton Kerr</t>
-        </is>
-      </c>
+          <t>Stirling Council</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>s.v.kerr@dundee.ac.uk</t>
+          <t>procurement@stirling.gov.uk</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>+44 1382386810</t>
+          <t>+44 1786404040</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>http://www.publiccontractsscotland.gov.uk</t>
+          <t>https://www.publictendersscotland.publiccontractsscotland.gov.uk</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
+          <t>Procurement, Teith House, Stirling, UKM77, FK7 7QA</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>UKM71, Dundee</t>
+          <t>UKM77</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -2465,19 +2704,111 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t>EV Infrastructure Back Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Trafford Council</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Tim Kulewa</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>tim.kulewa@star-procurement.gov.uk</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>+44 1619121616</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>http://www.trafford.gov.uk/</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>1st Floor, Trafford Town Hall, Stretford, M32 0TH</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Children and Young People's Residential Placements Flexible Procurement System (Round 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>University of Dundee</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Stewart Hamilton Kerr</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>s.v.kerr@dundee.ac.uk</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>+44 1382386810</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>http://www.publiccontractsscotland.gov.uk</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Procurement, 3rd Floor, Tower Building, Nethergate, Dundee, UKM71, DD1 4HN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>UKM71, Dundee</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
           <t>EV Charging Infrastructure</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
+  <autoFilter ref="A1:I13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2504,7 +2835,7 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>06 Oct 2026 06:18</t>
+          <t>06 Oct 2026 08:07</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2892,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">

--- a/docs/EPL_Tenders_latest.xlsx
+++ b/docs/EPL_Tenders_latest.xlsx
@@ -2835,7 +2835,7 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>06 Oct 2026 08:07</t>
+          <t>06 Oct 2026 08:35</t>
         </is>
       </c>
     </row>

--- a/docs/EPL_Tenders_latest.xlsx
+++ b/docs/EPL_Tenders_latest.xlsx
@@ -24473,7 +24473,7 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>06 Oct 2026 09:58</t>
+          <t>06 Oct 2026 10:10</t>
         </is>
       </c>
     </row>
